--- a/cet4/result/52_创业女神_商业女王的传奇/52_创业女神_商业女王的传奇_学习版.xlsx
+++ b/cet4/result/52_创业女神_商业女王的传奇/52_创业女神_商业女王的传奇_学习版.xlsx
@@ -397,717 +397,619 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D43"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>seaport</v>
       </c>
       <c r="B2" t="str">
-        <v>seaport</v>
+        <v>/ˈsiːpɔːrt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>海港</v>
       </c>
-      <c r="D2" t="str">
-        <v>seaport(海港)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>owner</v>
       </c>
       <c r="B3" t="str">
-        <v>owner</v>
+        <v>/ˈoʊnər/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>所有者</v>
       </c>
-      <c r="D3" t="str">
-        <v>owner(所有者)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>merchant</v>
       </c>
       <c r="B4" t="str">
-        <v>merchant</v>
+        <v>/ˈmɜːrtʃənt/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>商人</v>
       </c>
-      <c r="D4" t="str">
-        <v>merchant(商人)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>newspaper</v>
       </c>
       <c r="B5" t="str">
-        <v>newspaper</v>
+        <v>/ˈnuːzpeɪpər/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>报纸</v>
       </c>
-      <c r="D5" t="str">
-        <v>newspaper(报纸)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>technician</v>
       </c>
       <c r="B6" t="str">
-        <v>technician</v>
+        <v>/tekˈnɪʃn/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>技师</v>
       </c>
-      <c r="D6" t="str">
-        <v>technician(技师)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>wealth</v>
       </c>
       <c r="B7" t="str">
-        <v>wealth</v>
+        <v>/welθ/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>财富</v>
       </c>
-      <c r="D7" t="str">
-        <v>wealth(财富)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>vehicle</v>
       </c>
       <c r="B8" t="str">
-        <v>vehicle</v>
+        <v>/ˈviːəkl,ˈviːhɪkl/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>车辆</v>
       </c>
-      <c r="D8" t="str">
-        <v>vehicle(车辆)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>test</v>
       </c>
       <c r="B9" t="str">
-        <v>test</v>
+        <v>/test/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D9" t="str">
         <v>测验</v>
       </c>
-      <c r="D9" t="str">
-        <v>test(测验)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>destination</v>
       </c>
       <c r="B10" t="str">
-        <v>destination</v>
+        <v>/ˌdestɪˈneɪʃn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>目的地</v>
       </c>
-      <c r="D10" t="str">
-        <v>destination(目的地)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>enormous</v>
       </c>
       <c r="B11" t="str">
-        <v>enormous</v>
+        <v>/ɪˈnɔːrməs/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>巨大的</v>
       </c>
-      <c r="D11" t="str">
-        <v>enormous(巨大的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>mechanic</v>
       </c>
       <c r="B12" t="str">
-        <v>mechanic</v>
+        <v>/məˈkænɪk/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>技工</v>
       </c>
-      <c r="D12" t="str">
-        <v>mechanic(技工)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>laundry</v>
       </c>
       <c r="B13" t="str">
-        <v>laundry</v>
+        <v>/ˈlɔːndri/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>洗衣店</v>
       </c>
-      <c r="D13" t="str">
-        <v>laundry(洗衣店)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>typhoon</v>
       </c>
       <c r="B14" t="str">
-        <v>typhoon</v>
+        <v>/taɪˈfuːn/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>台风</v>
       </c>
-      <c r="D14" t="str">
-        <v>typhoon(台风)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>moisture</v>
       </c>
       <c r="B15" t="str">
-        <v>moisture</v>
+        <v>/ˈmɔɪstʃər/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>水分</v>
       </c>
-      <c r="D15" t="str">
-        <v>moisture(水分)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>define</v>
       </c>
       <c r="B16" t="str">
-        <v>enormous</v>
+        <v>/dɪˈfaɪn/</v>
       </c>
       <c r="C16" t="str">
-        <v>巨大的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D16" t="str">
-        <v>enormous(巨大的)📢</v>
+        <v>定义</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>learning</v>
       </c>
       <c r="B17" t="str">
-        <v>define</v>
+        <v>/ˈlɜːrnɪŋ/</v>
       </c>
       <c r="C17" t="str">
-        <v>定义</v>
+        <v>n./v.</v>
       </c>
       <c r="D17" t="str">
-        <v>define(定义)📢</v>
+        <v>学习</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>sequence</v>
       </c>
       <c r="B18" t="str">
-        <v>learning</v>
+        <v>/ˈsiːkwəns/</v>
       </c>
       <c r="C18" t="str">
-        <v>学习</v>
+        <v>n./vt.</v>
       </c>
       <c r="D18" t="str">
-        <v>learning(学习)📢</v>
+        <v>序列</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>novel</v>
       </c>
       <c r="B19" t="str">
-        <v>sequence</v>
+        <v>/ˈnɑːvl/</v>
       </c>
       <c r="C19" t="str">
-        <v>序列</v>
+        <v>n./adj.</v>
       </c>
       <c r="D19" t="str">
-        <v>sequence(序列)📢</v>
+        <v>新奇的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>bond</v>
       </c>
       <c r="B20" t="str">
-        <v>novel</v>
+        <v>/bɑːnd/</v>
       </c>
       <c r="C20" t="str">
-        <v>新奇的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D20" t="str">
-        <v>novel(新奇的)📢</v>
+        <v>债券</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>access</v>
       </c>
       <c r="B21" t="str">
-        <v>bond</v>
+        <v>/ˈækses/</v>
       </c>
       <c r="C21" t="str">
-        <v>债券</v>
+        <v>n./vt.</v>
       </c>
       <c r="D21" t="str">
-        <v>bond(债券)📢</v>
+        <v>通路</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>orange</v>
       </c>
       <c r="B22" t="str">
-        <v>access</v>
+        <v>/'ɔrɪndʒ/</v>
       </c>
       <c r="C22" t="str">
-        <v>通路</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>access(通路)📢</v>
+        <v>橙子</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>prisoner</v>
       </c>
       <c r="B23" t="str">
-        <v>orange</v>
+        <v>/ˈprɪznər/</v>
       </c>
       <c r="C23" t="str">
-        <v>橙子</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>orange(橙子)📢</v>
+        <v>囚犯</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>worthless</v>
       </c>
       <c r="B24" t="str">
-        <v>prisoner</v>
+        <v>/ˈwɜːrθləs/</v>
       </c>
       <c r="C24" t="str">
-        <v>囚犯</v>
+        <v>adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>prisoner(囚犯)📢</v>
+        <v>无价值的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>tuition</v>
       </c>
       <c r="B25" t="str">
-        <v>moisture</v>
+        <v>/tuˈɪʃn/</v>
       </c>
       <c r="C25" t="str">
-        <v>水分</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>moisture(水分)📢</v>
+        <v>学费</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>triangle</v>
       </c>
       <c r="B26" t="str">
-        <v>worthless</v>
+        <v>/ˈtraɪæŋɡl/</v>
       </c>
       <c r="C26" t="str">
-        <v>无价值的</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>worthless(无价值的)📢</v>
+        <v>三角形</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>battery</v>
       </c>
       <c r="B27" t="str">
-        <v>tuition</v>
+        <v>/ˈbætəri/</v>
       </c>
       <c r="C27" t="str">
-        <v>学费</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>tuition(学费)📢</v>
+        <v>电池</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>double</v>
       </c>
       <c r="B28" t="str">
-        <v>bond</v>
+        <v>/ˈdʌbl/</v>
       </c>
       <c r="C28" t="str">
-        <v>纽带</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>bond(纽带)📢</v>
+        <v>双重的</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>respectful</v>
       </c>
       <c r="B29" t="str">
-        <v>triangle</v>
+        <v>/rɪˈspektfl/</v>
       </c>
       <c r="C29" t="str">
-        <v>三角形</v>
+        <v>adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>triangle(三角形)📢</v>
+        <v>恭敬的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>even</v>
       </c>
       <c r="B30" t="str">
-        <v>battery</v>
+        <v>/ˈiːvn/</v>
       </c>
       <c r="C30" t="str">
-        <v>电池</v>
+        <v>n./vt./vi./v./adj./adv.</v>
       </c>
       <c r="D30" t="str">
-        <v>battery(电池)📢</v>
+        <v>甚至</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>fatigue</v>
       </c>
       <c r="B31" t="str">
-        <v>technician</v>
+        <v>/fəˈtiːɡ/</v>
       </c>
       <c r="C31" t="str">
-        <v>技师</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>technician(技师)📢</v>
+        <v>疲劳</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>bulb</v>
       </c>
       <c r="B32" t="str">
-        <v>double</v>
+        <v>/bʌlb/</v>
       </c>
       <c r="C32" t="str">
-        <v>双重的</v>
+        <v>n./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>double(双重的)📢</v>
+        <v>电灯泡</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>altitude</v>
       </c>
       <c r="B33" t="str">
-        <v>respectful</v>
+        <v>/ˈæltɪtuːd/</v>
       </c>
       <c r="C33" t="str">
-        <v>恭敬的</v>
+        <v>n.</v>
       </c>
       <c r="D33" t="str">
-        <v>respectful(恭敬的)📢</v>
+        <v>高度</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>sleep</v>
       </c>
       <c r="B34" t="str">
-        <v>even</v>
+        <v>/sliːp/</v>
       </c>
       <c r="C34" t="str">
-        <v>甚至</v>
+        <v>n./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>even(甚至)📢</v>
+        <v>睡觉</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>cover</v>
       </c>
       <c r="B35" t="str">
-        <v>fatigue</v>
+        <v>/ˈkʌvər/</v>
       </c>
       <c r="C35" t="str">
-        <v>疲劳</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>fatigue(疲劳)📢</v>
+        <v>覆盖</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>play</v>
       </c>
       <c r="B36" t="str">
-        <v>bulb</v>
+        <v>/pleɪ/</v>
       </c>
       <c r="C36" t="str">
-        <v>电灯泡</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>bulb(电灯泡)📢</v>
+        <v>游戏</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>interruption</v>
       </c>
       <c r="B37" t="str">
-        <v>altitude</v>
+        <v>/ˌɪntəˈrʌpʃn/</v>
       </c>
       <c r="C37" t="str">
-        <v>高度</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>altitude(高度)📢</v>
+        <v>中断</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>journey</v>
       </c>
       <c r="B38" t="str">
-        <v>sleep</v>
+        <v>/ˈdʒɜːrni/</v>
       </c>
       <c r="C38" t="str">
-        <v>睡觉</v>
+        <v>n./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>sleep(睡觉)📢</v>
+        <v>旅程</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>evening</v>
       </c>
       <c r="B39" t="str">
-        <v>cover</v>
+        <v>/ˈiːvnɪŋ/</v>
       </c>
       <c r="C39" t="str">
-        <v>覆盖</v>
+        <v>n./adj./int.</v>
       </c>
       <c r="D39" t="str">
-        <v>cover(覆盖)📢</v>
+        <v>晚上</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>stomach</v>
       </c>
       <c r="B40" t="str">
-        <v>play</v>
+        <v>/ˈstʌmək/</v>
       </c>
       <c r="C40" t="str">
-        <v>游戏</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>play(游戏)📢</v>
+        <v>胃</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>horizon</v>
       </c>
       <c r="B41" t="str">
-        <v>interruption</v>
+        <v>/həˈraɪzn/</v>
       </c>
       <c r="C41" t="str">
-        <v>中断</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>interruption(中断)📢</v>
+        <v>地平线</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>chew</v>
       </c>
       <c r="B42" t="str">
-        <v>journey</v>
+        <v>/tʃuː/</v>
       </c>
       <c r="C42" t="str">
-        <v>旅程</v>
+        <v>vt./v.</v>
       </c>
       <c r="D42" t="str">
-        <v>journey(旅程)📢</v>
+        <v>咀嚼</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>being</v>
       </c>
       <c r="B43" t="str">
-        <v>evening</v>
+        <v>/ˈbiːɪŋ/</v>
       </c>
       <c r="C43" t="str">
-        <v>晚上</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>evening(晚上)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>stomach</v>
-      </c>
-      <c r="C44" t="str">
-        <v>胃</v>
-      </c>
-      <c r="D44" t="str">
-        <v>stomach(胃)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>horizon</v>
-      </c>
-      <c r="C45" t="str">
-        <v>地平线</v>
-      </c>
-      <c r="D45" t="str">
-        <v>horizon(地平线)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>novel</v>
-      </c>
-      <c r="C46" t="str">
-        <v>小说</v>
-      </c>
-      <c r="D46" t="str">
-        <v>novel(小说)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>wealth</v>
-      </c>
-      <c r="C47" t="str">
-        <v>财富</v>
-      </c>
-      <c r="D47" t="str">
-        <v>wealth(财富)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>chew</v>
-      </c>
-      <c r="C48" t="str">
-        <v>咀嚼</v>
-      </c>
-      <c r="D48" t="str">
-        <v>chew(咀嚼)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>being</v>
-      </c>
-      <c r="C49" t="str">
         <v>存在</v>
-      </c>
-      <c r="D49" t="str">
-        <v>being(存在)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>altitude</v>
-      </c>
-      <c r="C50" t="str">
-        <v>高度</v>
-      </c>
-      <c r="D50" t="str">
-        <v>altitude(高度)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
   </ignoredErrors>
 </worksheet>
 </file>